--- a/dataset/results/model_choice.xlsx
+++ b/dataset/results/model_choice.xlsx
@@ -504,7 +504,7 @@
         <v>0.9579309402332361</v>
       </c>
       <c r="L2">
-        <v>12.57564115673761</v>
+        <v>12.49371428621337</v>
       </c>
     </row>
     <row r="3" spans="1:12">
@@ -542,7 +542,7 @@
         <v>0.915163929092045</v>
       </c>
       <c r="L3">
-        <v>0.6823835037164603</v>
+        <v>0.7015042524317261</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -580,7 +580,7 @@
         <v>0.9384647672844649</v>
       </c>
       <c r="L4">
-        <v>0.5132999577734551</v>
+        <v>0.4146196851852313</v>
       </c>
     </row>
     <row r="5" spans="1:12">
@@ -618,7 +618,7 @@
         <v>0.9131587424510621</v>
       </c>
       <c r="L5">
-        <v>2.560805484301986</v>
+        <v>2.381018708504035</v>
       </c>
     </row>
     <row r="6" spans="1:12">
@@ -656,7 +656,7 @@
         <v>0.9402966862765514</v>
       </c>
       <c r="L6">
-        <v>27.98684757638877</v>
+        <v>28.73126658225844</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -694,7 +694,7 @@
         <v>0.8772288890045814</v>
       </c>
       <c r="L7">
-        <v>0.9649897962851176</v>
+        <v>1.036365858521849</v>
       </c>
     </row>
     <row r="8" spans="1:12">
@@ -732,7 +732,7 @@
         <v>0.8986929274260725</v>
       </c>
       <c r="L8">
-        <v>13.93287266105259</v>
+        <v>13.50657759439546</v>
       </c>
     </row>
     <row r="9" spans="1:12">
@@ -770,7 +770,7 @@
         <v>0.819830929820908</v>
       </c>
       <c r="L9">
-        <v>1.376881164415077</v>
+        <v>1.48364838547472</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -808,7 +808,7 @@
         <v>0.874400477665556</v>
       </c>
       <c r="L10">
-        <v>1.406375212181523</v>
+        <v>1.461830145078183</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -846,7 +846,7 @@
         <v>0.6063001093294461</v>
       </c>
       <c r="L11">
-        <v>0.7356977034048838</v>
+        <v>0.7941736814963511</v>
       </c>
     </row>
     <row r="12" spans="1:12">
@@ -884,7 +884,7 @@
         <v>0.5178115889212828</v>
       </c>
       <c r="L12">
-        <v>1.216806759768996</v>
+        <v>1.130361606958265</v>
       </c>
     </row>
     <row r="13" spans="1:12">
@@ -922,7 +922,7 @@
         <v>0.5440051020408164</v>
       </c>
       <c r="L13">
-        <v>0.7406494473086865</v>
+        <v>0.7452064202422296</v>
       </c>
     </row>
   </sheetData>

--- a/dataset/results/model_choice.xlsx
+++ b/dataset/results/model_choice.xlsx
@@ -504,7 +504,7 @@
         <v>0.9579309402332361</v>
       </c>
       <c r="L2">
-        <v>12.49371428621337</v>
+        <v>13.03370089274159</v>
       </c>
     </row>
     <row r="3" spans="1:12">
@@ -542,7 +542,7 @@
         <v>0.915163929092045</v>
       </c>
       <c r="L3">
-        <v>0.7015042524317261</v>
+        <v>0.7018684107074447</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -580,7 +580,7 @@
         <v>0.9384647672844649</v>
       </c>
       <c r="L4">
-        <v>0.4146196851852313</v>
+        <v>0.4203127121270102</v>
       </c>
     </row>
     <row r="5" spans="1:12">
@@ -618,7 +618,7 @@
         <v>0.9131587424510621</v>
       </c>
       <c r="L5">
-        <v>2.381018708504035</v>
+        <v>2.447597575972358</v>
       </c>
     </row>
     <row r="6" spans="1:12">
@@ -656,7 +656,7 @@
         <v>0.9402966862765514</v>
       </c>
       <c r="L6">
-        <v>28.73126658225844</v>
+        <v>29.06318091121722</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -694,7 +694,7 @@
         <v>0.8772288890045814</v>
       </c>
       <c r="L7">
-        <v>1.036365858521849</v>
+        <v>1.132674533189758</v>
       </c>
     </row>
     <row r="8" spans="1:12">
@@ -732,7 +732,7 @@
         <v>0.8986929274260725</v>
       </c>
       <c r="L8">
-        <v>13.50657759439546</v>
+        <v>14.10902763580168</v>
       </c>
     </row>
     <row r="9" spans="1:12">
@@ -770,7 +770,7 @@
         <v>0.819830929820908</v>
       </c>
       <c r="L9">
-        <v>1.48364838547472</v>
+        <v>1.248580782371732</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -808,7 +808,7 @@
         <v>0.874400477665556</v>
       </c>
       <c r="L10">
-        <v>1.461830145078183</v>
+        <v>1.541271470988763</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -846,7 +846,7 @@
         <v>0.6063001093294461</v>
       </c>
       <c r="L11">
-        <v>0.7941736814963511</v>
+        <v>0.6784360121069817</v>
       </c>
     </row>
     <row r="12" spans="1:12">
@@ -884,7 +884,7 @@
         <v>0.5178115889212828</v>
       </c>
       <c r="L12">
-        <v>1.130361606958265</v>
+        <v>1.109312499781425</v>
       </c>
     </row>
     <row r="13" spans="1:12">
@@ -922,7 +922,7 @@
         <v>0.5440051020408164</v>
       </c>
       <c r="L13">
-        <v>0.7452064202422296</v>
+        <v>0.7763892426737584</v>
       </c>
     </row>
   </sheetData>

--- a/dataset/results/model_choice.xlsx
+++ b/dataset/results/model_choice.xlsx
@@ -504,7 +504,7 @@
         <v>0.9579309402332361</v>
       </c>
       <c r="L2">
-        <v>13.03370089274159</v>
+        <v>12.920346938588</v>
       </c>
     </row>
     <row r="3" spans="1:12">
@@ -542,7 +542,7 @@
         <v>0.915163929092045</v>
       </c>
       <c r="L3">
-        <v>0.7018684107074447</v>
+        <v>0.678130952425762</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -580,7 +580,7 @@
         <v>0.9384647672844649</v>
       </c>
       <c r="L4">
-        <v>0.4203127121270102</v>
+        <v>0.4230769557697614</v>
       </c>
     </row>
     <row r="5" spans="1:12">
@@ -618,7 +618,7 @@
         <v>0.9131587424510621</v>
       </c>
       <c r="L5">
-        <v>2.447597575972358</v>
+        <v>2.556464710865146</v>
       </c>
     </row>
     <row r="6" spans="1:12">
@@ -656,7 +656,7 @@
         <v>0.9402966862765514</v>
       </c>
       <c r="L6">
-        <v>29.06318091121722</v>
+        <v>27.9137967685974</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -694,7 +694,7 @@
         <v>0.8772288890045814</v>
       </c>
       <c r="L7">
-        <v>1.132674533189758</v>
+        <v>1.173045280684535</v>
       </c>
     </row>
     <row r="8" spans="1:12">
@@ -732,7 +732,7 @@
         <v>0.8986929274260725</v>
       </c>
       <c r="L8">
-        <v>14.10902763580168</v>
+        <v>13.1253071855303</v>
       </c>
     </row>
     <row r="9" spans="1:12">
@@ -770,7 +770,7 @@
         <v>0.819830929820908</v>
       </c>
       <c r="L9">
-        <v>1.248580782371732</v>
+        <v>1.364061649435665</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -808,7 +808,7 @@
         <v>0.874400477665556</v>
       </c>
       <c r="L10">
-        <v>1.541271470988763</v>
+        <v>1.413612457494013</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -846,7 +846,7 @@
         <v>0.6063001093294461</v>
       </c>
       <c r="L11">
-        <v>0.6784360121069817</v>
+        <v>0.7839581206123704</v>
       </c>
     </row>
     <row r="12" spans="1:12">
@@ -884,7 +884,7 @@
         <v>0.5178115889212828</v>
       </c>
       <c r="L12">
-        <v>1.109312499781425</v>
+        <v>1.849521258624801</v>
       </c>
     </row>
     <row r="13" spans="1:12">
@@ -922,7 +922,7 @@
         <v>0.5440051020408164</v>
       </c>
       <c r="L13">
-        <v>0.7763892426737584</v>
+        <v>0.7324313351617303</v>
       </c>
     </row>
   </sheetData>

--- a/dataset/results/model_choice.xlsx
+++ b/dataset/results/model_choice.xlsx
@@ -504,7 +504,7 @@
         <v>0.9579309402332361</v>
       </c>
       <c r="L2">
-        <v>12.920346938588</v>
+        <v>12.58442006826731</v>
       </c>
     </row>
     <row r="3" spans="1:12">
@@ -542,7 +542,7 @@
         <v>0.915163929092045</v>
       </c>
       <c r="L3">
-        <v>0.678130952425762</v>
+        <v>0.6950248721945432</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -580,7 +580,7 @@
         <v>0.9384647672844649</v>
       </c>
       <c r="L4">
-        <v>0.4230769557697614</v>
+        <v>0.4459555695427057</v>
       </c>
     </row>
     <row r="5" spans="1:12">
@@ -618,7 +618,7 @@
         <v>0.9131587424510621</v>
       </c>
       <c r="L5">
-        <v>2.556464710865146</v>
+        <v>2.453133078199776</v>
       </c>
     </row>
     <row r="6" spans="1:12">
@@ -656,7 +656,7 @@
         <v>0.9402966862765514</v>
       </c>
       <c r="L6">
-        <v>27.9137967685974</v>
+        <v>27.98195344387002</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -694,7 +694,7 @@
         <v>0.8772288890045814</v>
       </c>
       <c r="L7">
-        <v>1.173045280684535</v>
+        <v>1.565897321529674</v>
       </c>
     </row>
     <row r="8" spans="1:12">
@@ -732,7 +732,7 @@
         <v>0.8986929274260725</v>
       </c>
       <c r="L8">
-        <v>13.1253071855303</v>
+        <v>13.09620408243731</v>
       </c>
     </row>
     <row r="9" spans="1:12">
@@ -770,7 +770,7 @@
         <v>0.819830929820908</v>
       </c>
       <c r="L9">
-        <v>1.364061649435665</v>
+        <v>1.483711096913182</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -808,7 +808,7 @@
         <v>0.874400477665556</v>
       </c>
       <c r="L10">
-        <v>1.413612457494013</v>
+        <v>1.44539774669438</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -846,7 +846,7 @@
         <v>0.6063001093294461</v>
       </c>
       <c r="L11">
-        <v>0.7839581206123704</v>
+        <v>0.8782801870085901</v>
       </c>
     </row>
     <row r="12" spans="1:12">
@@ -884,7 +884,7 @@
         <v>0.5178115889212828</v>
       </c>
       <c r="L12">
-        <v>1.849521258624801</v>
+        <v>2.434784650962634</v>
       </c>
     </row>
     <row r="13" spans="1:12">
@@ -922,7 +922,7 @@
         <v>0.5440051020408164</v>
       </c>
       <c r="L13">
-        <v>0.7324313351617303</v>
+        <v>0.7692623292772079</v>
       </c>
     </row>
   </sheetData>

--- a/dataset/results/model_choice.xlsx
+++ b/dataset/results/model_choice.xlsx
@@ -504,7 +504,7 @@
         <v>0.9579309402332361</v>
       </c>
       <c r="L2">
-        <v>12.58442006826731</v>
+        <v>12.40933099578716</v>
       </c>
     </row>
     <row r="3" spans="1:12">
@@ -542,7 +542,7 @@
         <v>0.915163929092045</v>
       </c>
       <c r="L3">
-        <v>0.6950248721945432</v>
+        <v>0.6465116916378789</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -580,7 +580,7 @@
         <v>0.9384647672844649</v>
       </c>
       <c r="L4">
-        <v>0.4459555695427057</v>
+        <v>0.460725977725716</v>
       </c>
     </row>
     <row r="5" spans="1:12">
@@ -618,7 +618,7 @@
         <v>0.9131587424510621</v>
       </c>
       <c r="L5">
-        <v>2.453133078199776</v>
+        <v>3.122043154553776</v>
       </c>
     </row>
     <row r="6" spans="1:12">
@@ -656,7 +656,7 @@
         <v>0.9402966862765514</v>
       </c>
       <c r="L6">
-        <v>27.98195344387002</v>
+        <v>28.57940901290918</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -694,7 +694,7 @@
         <v>0.8772288890045814</v>
       </c>
       <c r="L7">
-        <v>1.565897321529674</v>
+        <v>0.923535076501238</v>
       </c>
     </row>
     <row r="8" spans="1:12">
@@ -732,7 +732,7 @@
         <v>0.8986929274260725</v>
       </c>
       <c r="L8">
-        <v>13.09620408243731</v>
+        <v>13.35195599485629</v>
       </c>
     </row>
     <row r="9" spans="1:12">
@@ -770,7 +770,7 @@
         <v>0.819830929820908</v>
       </c>
       <c r="L9">
-        <v>1.483711096913182</v>
+        <v>1.279697065521239</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -808,7 +808,7 @@
         <v>0.874400477665556</v>
       </c>
       <c r="L10">
-        <v>1.44539774669438</v>
+        <v>1.59960267855964</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -846,7 +846,7 @@
         <v>0.6063001093294461</v>
       </c>
       <c r="L11">
-        <v>0.8782801870085901</v>
+        <v>0.7473273812212603</v>
       </c>
     </row>
     <row r="12" spans="1:12">
@@ -884,7 +884,7 @@
         <v>0.5178115889212828</v>
       </c>
       <c r="L12">
-        <v>2.434784650962634</v>
+        <v>1.161884991072956</v>
       </c>
     </row>
     <row r="13" spans="1:12">
@@ -922,7 +922,7 @@
         <v>0.5440051020408164</v>
       </c>
       <c r="L13">
-        <v>0.7692623292772079</v>
+        <v>0.7360178563672258</v>
       </c>
     </row>
   </sheetData>
